--- a/VerveStacks_KEN/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_KEN/SuppXLS/Scen_Base_VS.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{922945E2-FB99-4DCA-A561-BA2891145D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCE4B8F7-ED0E-4811-B66B-CBA0232B3170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
     <sheet name="buildrates" sheetId="4" r:id="rId3"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="121">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -390,6 +390,9 @@
     <t>\I: hydro</t>
   </si>
   <si>
+    <t>UCE_min oil fleet utilization</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -495,8 +498,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -624,7 +628,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -637,6 +641,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -978,6 +983,616 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62139914-22D2-4E05-8D8E-824B7833E931}">
+  <dimension ref="B9:L26"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12">
+        <v>0.67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14">
+        <v>1.67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15">
+        <v>2.67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16">
+        <v>3.67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J17" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18">
+        <v>8.07</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19">
+        <v>6.6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J20" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21">
+        <v>3.67</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J21" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22">
+        <v>11.11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J22" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>24.44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25">
+        <v>33.33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J25" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26">
+        <v>11.11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" t="s">
+        <v>107</v>
+      </c>
+      <c r="I26" s="13">
+        <v>45283</v>
+      </c>
+      <c r="J26" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1008,7 +1623,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1113,7 +1728,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1359,10 +1974,34 @@
       <c r="J10" s="3">
         <v>0.22132714596479999</v>
       </c>
+      <c r="AF10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>0.10772396938709886</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AI10*$AD$1</f>
+        <v>2.1544793877419772E-2</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>0.11415525114155252</v>
@@ -1690,616 +2329,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BB888B-C81A-4794-B0BD-2D2BFB1DEB7B}">
-  <dimension ref="B9:L26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12">
-        <v>0.67</v>
-      </c>
-      <c r="F12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J12" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J13" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14">
-        <v>1.67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15">
-        <v>2.67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16">
-        <v>3.67</v>
-      </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J16" t="s">
-        <v>107</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B17">
-        <v>2030</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B18">
-        <v>2030</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18">
-        <v>8.07</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J18" t="s">
-        <v>107</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <v>2030</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19">
-        <v>6.6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J19" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B20">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J20" t="s">
-        <v>107</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B21">
-        <v>2030</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21">
-        <v>3.67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B22">
-        <v>2030</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22">
-        <v>11.11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" t="s">
-        <v>105</v>
-      </c>
-      <c r="H22" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <v>2030</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23">
-        <v>24.44</v>
-      </c>
-      <c r="F23" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H23" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <v>2030</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J24" t="s">
-        <v>107</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B25">
-        <v>2030</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25">
-        <v>33.33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>2030</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26">
-        <v>11.11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="12">
-        <v>45283</v>
-      </c>
-      <c r="J26" t="s">
-        <v>107</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2322,12 +2351,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2356,7 +2385,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -5821,7 +5850,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B250">
         <v>2000</v>
@@ -5947,7 +5976,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B259">
         <v>2001</v>
@@ -6073,7 +6102,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B268">
         <v>2002</v>
@@ -6199,7 +6228,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B277">
         <v>2003</v>
@@ -6325,7 +6354,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B286">
         <v>2004</v>
@@ -6451,7 +6480,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B295">
         <v>2005</v>
@@ -6577,7 +6606,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B304">
         <v>2006</v>
@@ -6703,7 +6732,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B313">
         <v>2007</v>
@@ -6829,7 +6858,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B322">
         <v>2008</v>
@@ -6955,7 +6984,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -7081,7 +7110,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B340">
         <v>2010</v>
@@ -7207,7 +7236,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B349">
         <v>2011</v>
@@ -7333,7 +7362,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B358">
         <v>2012</v>
@@ -7459,7 +7488,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B367">
         <v>2013</v>
@@ -7585,7 +7614,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B376">
         <v>2014</v>
@@ -7711,7 +7740,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B385">
         <v>2015</v>
@@ -7837,7 +7866,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B394">
         <v>2016</v>
@@ -7963,7 +7992,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B403">
         <v>2017</v>
@@ -8089,7 +8118,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B412">
         <v>2018</v>
@@ -8215,7 +8244,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B421">
         <v>2019</v>
@@ -8341,7 +8370,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B430">
         <v>2020</v>
@@ -8467,7 +8496,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B439">
         <v>2021</v>
@@ -8593,7 +8622,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B448">
         <v>2022</v>
@@ -8719,7 +8748,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -9265,7 +9294,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B496">
         <v>2018</v>
@@ -9279,7 +9308,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B497">
         <v>2019</v>
@@ -9293,7 +9322,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B498">
         <v>2020</v>
@@ -9307,7 +9336,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B499">
         <v>2021</v>
@@ -9321,7 +9350,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B500">
         <v>2022</v>
@@ -9335,7 +9364,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B501">
         <v>2023</v>
@@ -9349,7 +9378,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B502">
         <v>2024</v>
@@ -9363,7 +9392,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B503">
         <v>2011</v>
@@ -9377,7 +9406,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B504">
         <v>2012</v>
@@ -9391,7 +9420,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B505">
         <v>2013</v>
@@ -9405,7 +9434,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B506">
         <v>2014</v>
@@ -9419,7 +9448,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B507">
         <v>2015</v>
@@ -9433,7 +9462,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B508">
         <v>2016</v>
@@ -9447,7 +9476,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B509">
         <v>2017</v>
@@ -9461,7 +9490,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B510">
         <v>2004</v>
@@ -9475,7 +9504,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B511">
         <v>2005</v>
@@ -9489,7 +9518,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B512">
         <v>2006</v>
@@ -9503,7 +9532,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B513">
         <v>2007</v>
@@ -9517,7 +9546,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9531,7 +9560,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B515">
         <v>2009</v>
@@ -9545,7 +9574,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B516">
         <v>2010</v>
@@ -9559,7 +9588,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B517">
         <v>2000</v>
@@ -9573,7 +9602,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B518">
         <v>2001</v>
@@ -9587,7 +9616,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B519">
         <v>2002</v>
@@ -9601,7 +9630,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B520">
         <v>2003</v>
@@ -9615,7 +9644,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B521">
         <v>2002</v>
@@ -9629,7 +9658,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B522">
         <v>2003</v>
@@ -9643,7 +9672,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B523">
         <v>2004</v>
@@ -9657,7 +9686,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B524">
         <v>2005</v>
@@ -9671,7 +9700,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B525">
         <v>2006</v>
@@ -9685,7 +9714,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B526">
         <v>2007</v>
@@ -9699,7 +9728,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B527">
         <v>2008</v>
@@ -9713,7 +9742,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B528">
         <v>2009</v>
@@ -9727,7 +9756,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B529">
         <v>2010</v>
@@ -9741,7 +9770,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B530">
         <v>2011</v>
@@ -9755,7 +9784,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B531">
         <v>2012</v>
@@ -9769,7 +9798,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B532">
         <v>2013</v>
@@ -9783,7 +9812,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B533">
         <v>2014</v>
@@ -9797,7 +9826,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B534">
         <v>2015</v>
@@ -9811,7 +9840,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B535">
         <v>2016</v>
@@ -9825,7 +9854,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B536">
         <v>2017</v>
@@ -9839,7 +9868,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B537">
         <v>2018</v>
@@ -9853,7 +9882,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B538">
         <v>2019</v>
@@ -9867,7 +9896,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B539">
         <v>2020</v>
@@ -9881,7 +9910,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B540">
         <v>2021</v>
@@ -9895,7 +9924,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B541">
         <v>2022</v>
@@ -9909,7 +9938,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B542">
         <v>2000</v>
@@ -9923,7 +9952,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B543">
         <v>2001</v>
@@ -11001,7 +11030,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B620">
         <v>2018</v>
@@ -11015,7 +11044,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B621">
         <v>2019</v>
@@ -11029,7 +11058,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -11043,7 +11072,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B623">
         <v>2021</v>
@@ -11057,7 +11086,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B624">
         <v>2022</v>
@@ -11071,7 +11100,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B625">
         <v>2023</v>
@@ -11085,7 +11114,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B626">
         <v>2024</v>
@@ -11099,7 +11128,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B627">
         <v>2011</v>
@@ -11113,7 +11142,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B628">
         <v>2012</v>
@@ -11127,7 +11156,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B629">
         <v>2013</v>
@@ -11141,7 +11170,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B630">
         <v>2014</v>
@@ -11155,7 +11184,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2015</v>
@@ -11169,7 +11198,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B632">
         <v>2016</v>
@@ -11183,7 +11212,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B633">
         <v>2017</v>
@@ -11197,7 +11226,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B634">
         <v>2004</v>
@@ -11211,7 +11240,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B635">
         <v>2005</v>
@@ -11225,7 +11254,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B636">
         <v>2006</v>
@@ -11239,7 +11268,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B637">
         <v>2007</v>
@@ -11253,7 +11282,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B638">
         <v>2008</v>
@@ -11267,7 +11296,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B639">
         <v>2009</v>
@@ -11281,7 +11310,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2010</v>
@@ -11295,7 +11324,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B641">
         <v>2000</v>
@@ -11309,7 +11338,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B642">
         <v>2001</v>
@@ -11323,7 +11352,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B643">
         <v>2002</v>
@@ -11337,7 +11366,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B644">
         <v>2003</v>
@@ -11351,7 +11380,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B645">
         <v>2002</v>
@@ -11365,7 +11394,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B646">
         <v>2003</v>
@@ -11379,7 +11408,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B647">
         <v>2004</v>
@@ -11393,7 +11422,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B648">
         <v>2005</v>
@@ -11407,7 +11436,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2006</v>
@@ -11421,7 +11450,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B650">
         <v>2007</v>
@@ -11435,7 +11464,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B651">
         <v>2008</v>
@@ -11449,7 +11478,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B652">
         <v>2009</v>
@@ -11463,7 +11492,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B653">
         <v>2010</v>
@@ -11477,7 +11506,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B654">
         <v>2011</v>
@@ -11491,7 +11520,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B655">
         <v>2012</v>
@@ -11505,7 +11534,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B656">
         <v>2013</v>
@@ -11519,7 +11548,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B657">
         <v>2014</v>
@@ -11533,7 +11562,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B658">
         <v>2015</v>
@@ -11547,7 +11576,7 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B659">
         <v>2016</v>
@@ -11561,7 +11590,7 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B660">
         <v>2017</v>
@@ -11575,7 +11604,7 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B661">
         <v>2018</v>
@@ -11589,7 +11618,7 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B662">
         <v>2019</v>
@@ -11603,7 +11632,7 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B663">
         <v>2020</v>
@@ -11617,7 +11646,7 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B664">
         <v>2021</v>
@@ -11631,7 +11660,7 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B665">
         <v>2022</v>
@@ -11645,7 +11674,7 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B666">
         <v>2000</v>
@@ -11659,7 +11688,7 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B667">
         <v>2001</v>
